--- a/VarsityHub_Feature_Matrix_v6_updated.xlsx
+++ b/VarsityHub_Feature_Matrix_v6_updated.xlsx
@@ -6446,17 +6446,22 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Rookie: 2 pending max; Veteran+: unlimited</t>
+          <t>3 pending max for ALL non-auto-approved creators. No plan exception — auto-approve is role-based (coach/admin), not plan-based.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Wrong → Fixed</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>ALL FANS CAN PITCH EVENTS TO ANY TEAM. ITS UP TO EMAIL ADMIN TO APPROVE</t>
+          <t>CORRECTED: events.ts:780 pendingCount &gt;= 3. Error msg says "Upgrade to Veteran" but code has NO plan check. Coach/admin auto-approve bypasses cap via role, not plan.</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>FIXED v6 update</t>
         </is>
       </c>
     </row>
@@ -6983,22 +6988,22 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Must be within 2km of event; error msg updated</t>
+          <t>Stories: 1km geofence. Posts: 3km geofence. Neither is 2km.</t>
         </is>
       </c>
       <c r="J102" s="28" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Wrong → Fixed</t>
         </is>
       </c>
       <c r="K102" s="10" t="inlineStr">
         <is>
-          <t>Server enforces 2km geofence for game stories. User spec: same 2km radius applies to posts tagged to a game.</t>
+          <t>CORRECTED: geofencing.ts:235 stories=1km, geofencing.ts:337 posts=3km. Old spec said 2km — code never matched.</t>
         </is>
       </c>
       <c r="L102" s="29" t="inlineStr">
         <is>
-          <t>ACCURATE: unchanged</t>
+          <t>FIXED v6 update</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7215,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7230,12 +7235,17 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Wrong → Fixed</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Confirmed: No role-based DM restrictions in messages.ts. All authenticated users can DM based on recipient dm_policy preference (everyone/following/no_one). No Email Admin or Org Owner block.</t>
+          <t>CORRECTED: messages.ts gates DMs on requireAuth + recipient dm_policy only. Zero role-based restrictions. All authenticated users can send DMs regardless of role. Email Admin, Org Owner, Super Admin all have full DM access.</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>FIXED v6 update</t>
         </is>
       </c>
     </row>
@@ -7937,7 +7947,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ad radius: 10km</t>
+          <t>Ad radius: 9km</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7977,7 +7987,17 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Wrong → Fixed</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>CORRECTED: ads.ts:207 hardcodes radius: 9. Was "10km" in spec. Feed filtering also uses 9km (ads.ts:515).</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>FIXED v6 update</t>
         </is>
       </c>
     </row>
@@ -8137,7 +8157,17 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>BROKEN</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>BLOCKED: sendAdApprovedEmail() calls blockUnapprovedEmail("AD_APPROVED") at email.ts:226. Email NEVER sends. Push notification still works. Creator must open app to see approval status.</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>BLOCKED — v6 update</t>
         </is>
       </c>
     </row>
@@ -14614,17 +14644,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8 pending max</t>
+          <t>3 pending max</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlimited </t>
+          <t>3 pending max*</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Unlimited</t>
+          <t>3 pending max*</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -14634,7 +14664,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALL FAN EVENTS HAVE TO GO THROUGH THE SAME APPROVAL PROCESS NO MATTER WAT TIER THE COACH IS </t>
+          <t>CORRECTED: Code enforces 3-cap for ALL non-auto-approved creators (events.ts:780). No plan-based exception exists — auto-approve is role-based (coach/admin), not plan-based. Error msg at events.ts:790 misleadingly says "Upgrade to Veteran" but code never checks plan. *Coaches bypass cap entirely via auto-approve, not plan tier.</t>
         </is>
       </c>
     </row>
@@ -14732,22 +14762,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10km</t>
+          <t>9km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10km</t>
+          <t>9km</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10km</t>
+          <t>9km</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Wrong → Fixed</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CORRECTED: ads.ts:207 hardcodes radius: 9. Was 10km in prior spec.</t>
         </is>
       </c>
     </row>
@@ -14917,7 +14952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15181,7 +15216,7 @@
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t>ads.ts:180</t>
+          <t>ads.ts:207 (shifted from 180 after ad paywall code added)</t>
         </is>
       </c>
     </row>
@@ -15315,6 +15350,226 @@
       <c r="D19" t="inlineStr">
         <is>
           <t>posts.ts:1808</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Plan Comparison R8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8 pending max for Rookie</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>WRONG — code is 3 pending max (events.ts:780). No plan differentiation — cap applies to ALL non-auto-approved creators equally.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>events.ts:774-792</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Plan Comparison R12</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ad radius = 10km</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>WRONG — ads.ts:207 hardcodes radius: 9 (9km). Cell not updated in prior correction pass.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ads.ts:207 (shifted from 180 after ad paywall code added)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Feature Matrix R91</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rookie: 2 pending max; Veteran+: unlimited</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>WRONG on both counts. Cap is 3, not 2. No plan exception exists — auto-approve is role-based (coach/admin), not plan-based. A Veteran fan still hits the 3-cap. Error msg misleadingly says "Upgrade to Veteran".</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>events.ts:774-797</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Feature Matrix R102</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Geofence = 2km</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>WRONG — Stories = 1km (geofencing.ts:235), Posts = 3km (geofencing.ts:337). 2km never existed in code.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>geofencing.ts:235, :337</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Feature Matrix R108</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Email Admin / Org Owner / Super Admin DMs = N</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>WRONG — DMs gated on requireAuth + dm_policy only (messages.ts:145-149, :259-276). Zero role-based restrictions. All should be Y.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>messages.ts:145, :260</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Approval Process Audit</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Line numbers in ads.ts shifted after ad paywall fix</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ads.ts line numbers shifted: radius now at line 207 (was 180). V6 Corrections R12 evidence column updated.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ads.ts:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Feature Matrix R124</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ad radius: 10km</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>WRONG — now corrected in main tab to 9km. ads.ts:207.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ads.ts:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Feature Matrix R127</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ad approval email includes receipt details — marked Y/Accurate</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>WRONG — sendAdApprovedEmail() is BLOCKED by blockUnapprovedEmail() at email.ts:226. Email never sends. Now marked BROKEN in main tab.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>email.ts:226</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Full Codebase Audit R6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Root cause listed as missing env vars / SendGrid failures</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>WRONG root cause — real cause is blockUnapprovedEmail() intentionally killing emails at code level, not missing env vars. Updated in main tab.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>email.ts:158</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Plan Comparison R8 C8/D8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Veteran/Legend get "Unlimited" pending events</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>WRONG — code enforces same 3-cap for all non-auto-approved. Auto-approve is role-based not plan-based. events.ts:790 has misleading copy.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>events.ts:774-797</t>
         </is>
       </c>
     </row>
@@ -19210,12 +19465,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Fire-and-forget sends swallow SendGrid failures. If Railway env vars missing, emails drop silently.</t>
+          <t>ROOT CAUSE: blockUnapprovedEmail() in email.ts:158 silently kills 9 email types. Not a missing env var issue — the function intentionally returns false before reaching SendGrid. Coach/event emails work because they use sendTemplateEmail directly.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Verify Railway SENDGRID_API_KEY + template IDs. Add /health/email boot check. Log failures at error level.</t>
+          <t>Fix: Replace blockUnapprovedEmail() calls with sendTemplateEmail() for the 7 emails that have existing SendGrid templates. Do NOT create new templates or new email types.</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21656,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>BROKEN / PARTIAL</t>
+          <t>BROKEN — ROOT CAUSE IDENTIFIED</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -21411,12 +21666,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>server/src/routes/ads.ts:260-272 → email.ts:526-531. Fire-and-forget; if SENDGRID_API_KEY or AD_PENDING_REVIEW template ID is missing on Railway, email silently drops (warning logged only). approvalService.ts:252-129 uses .catch(()=&gt;{}) to silence all failures.</t>
+          <t>ROOT CAUSE: email.ts:158 blockUnapprovedEmail() silently blocks 9 email types (AD_PENDING_REVIEW at :197, AD_APPROVED at :226, AD_REJECTED at :237, LEAGUE_APPROVED at :790, LEAGUE_REJECTED at :806, ADMIN_ACTION_CONFIRMATION at :889, BILLING_NOTICE at :631, GENERIC_EMAIL at :175, ABUSE_REPORT at :214). These functions return false before reaching SendGrid. Push notifications still work for most flows.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1) Verify Railway has SENDGRID_API_KEY + all template IDs (AD_PENDING_REVIEW, LEAGUE_PENDING_APPROVAL, COACH_APPROVED, JOIN_REQUEST, VERIFICATION). 2) Add a /health/email endpoint that checks SendGrid connectivity at boot. 3) Log email failures to Sentry with severity=error, not just warn.</t>
+          <t>Fix: Replace blockUnapprovedEmail() calls in the 7 approval-related emails with sendTemplateEmail() using existing TEMPLATE_IDS. Coach approval and event emails are NOT affected — they already use sendTemplateEmail directly.</t>
         </is>
       </c>
     </row>
@@ -21566,7 +21821,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Runtime QA: (a) search returns nearby orgs, (b) selecting an org emails that org admin (depends on Finding #1 email fix), (c) create new triggers super-admin approval email. If email fix (Finding #1) lands first, this flow should work.</t>
+          <t>Runtime QA: (a) search returns nearby orgs, (b) selecting an org emails that org admin — THIS WORKS (COACH_JOIN_REQUEST uses sendTemplateEmail). (c) create new triggers super-admin approval email — THIS WORKS (LEAGUE_APPROVAL_REQUEST uses sendTemplateEmail). Note: admin RESPONSE emails (approve/reject) are BLOCKED by blockUnapprovedEmail().</t>
         </is>
       </c>
     </row>
